--- a/02_DIA_inicio_2026_analisis_assets/rbd_9701_liceo-polivalente-olof-palme_nt1_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9701_liceo-polivalente-olof-palme_nt1_nucleos.xlsx
@@ -679,13 +679,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B603449-9501-42DF-9396-39403EF51FAE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F934EE8D-3FDD-4130-9482-0265B9143F3E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F8FAD7F-C5E0-46F9-938C-38021885F1F2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5FF06FE-281E-4A04-8E8B-0526032085DE}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C096993E-1B7D-414E-8F22-1CFA0B4656C4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{49521F8C-CA7E-426A-93FD-82E292FC22CF}"/>
 </file>